--- a/assets/constructions/examples/ctd_tsmb_tuplechamfer_preparting.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_tuplechamfer_preparting.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,11 +624,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4.0SIR0.2LCHAMFER-0VMX</t>
+          <t>4.0SIR0.2MCHAMFER-0VMX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -674,13 +699,13 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
@@ -743,11 +768,22 @@
           <t>2018/VARGUS 2018 General Catalog</t>
         </is>
       </c>
+      <c r="AN2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6.0SIR0.2SCHAMFER-0VMX</t>
+          <t>4.0SIR0.2LCHAMFER-0VMX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -768,7 +804,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VAR_6SI02</t>
+          <t>VAR_4SI02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -777,37 +813,37 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>2.92</v>
+        <v>1.92</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="O3" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="P3" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="U3" t="n">
         <v>0.2</v>
@@ -825,7 +861,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>VARGUS_6SI02</t>
+          <t>VARGUS_4SI02</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -862,11 +898,22 @@
           <t>2018/VARGUS 2018 General Catalog</t>
         </is>
       </c>
+      <c r="AN3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4.0SIR0.2MCHAMFER-0VMX</t>
+          <t>4.0SIR0.2SCHAMFER-0VMX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -912,13 +959,13 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="P4" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
@@ -981,6 +1028,17 @@
           <t>2018/VARGUS 2018 General Catalog</t>
         </is>
       </c>
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1100,11 +1158,22 @@
           <t>2018/VARGUS 2018 General Catalog</t>
         </is>
       </c>
+      <c r="AN5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6.0SIR0.2MCHAMFER-0VMX</t>
+          <t>6.0SIR0.2SCHAMFER-0VMX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1150,13 +1219,13 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="P6" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
@@ -1219,6 +1288,17 @@
           <t>2018/VARGUS 2018 General Catalog</t>
         </is>
       </c>
+      <c r="AN6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
